--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486769_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486769_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.9534</v>
+        <v>9.8751</v>
       </c>
       <c r="E2" t="n">
-        <v>10.2827</v>
+        <v>9.303699999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6707</v>
+        <v>0.5714</v>
       </c>
       <c r="G2" t="n">
         <v>5.307</v>
@@ -610,13 +610,13 @@
         <v>2.3169</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1678</v>
+        <v>1.0894</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2612</v>
+        <v>1.2821</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0934</v>
+        <v>-0.1927</v>
       </c>
       <c r="V2" t="n">
         <v>2.1271</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1357</v>
+        <v>3.5645</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3861</v>
+        <v>2.0136</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7496</v>
+        <v>1.551</v>
       </c>
       <c r="G3" t="n">
         <v>1.6027</v>
@@ -688,13 +688,13 @@
         <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0495</v>
+        <v>0.3793</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5243</v>
+        <v>0.1032</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4748</v>
+        <v>0.2761</v>
       </c>
       <c r="V3" t="n">
         <v>2.741</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.728</v>
+        <v>3.0065</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7665</v>
+        <v>4.6973</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0384</v>
+        <v>-1.6908</v>
       </c>
       <c r="G4" t="n">
         <v>3.7035</v>
@@ -766,13 +766,13 @@
         <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8716</v>
+        <v>0.4068</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5243</v>
+        <v>0.4065</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3474</v>
+        <v>0.0003</v>
       </c>
       <c r="V4" t="n">
         <v>-2.4554</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SANTOLARIA MARTIN</t>
+          <t>I. IBAÑEZ ZAMALLOA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4343</v>
+        <v>1.616</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1242</v>
+        <v>-0.7965</v>
       </c>
       <c r="F5" t="n">
-        <v>0.31</v>
+        <v>2.4125</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2137</v>
+        <v>-0.4734</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1586</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.945</v>
+        <v>-0.5628</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6761</v>
+        <v>0.1074</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6761</v>
+        <v>0.2971</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.1897</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4624</v>
+        <v>-0.5808</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4826</v>
+        <v>-0.2077</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.945</v>
+        <v>-0.3731</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7723</v>
+        <v>2.51</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4137</v>
+        <v>1.5102</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4136</v>
+        <v>1.0269</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0001</v>
+        <v>0.4833</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4285</v>
+        <v>1.3306</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4824</v>
+        <v>-0.5306</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9109</v>
+        <v>1.8613</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3643</v>
@@ -922,13 +922,13 @@
         <v>0.7723</v>
       </c>
       <c r="S6" t="n">
-        <v>1.6769</v>
+        <v>1.579</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7718</v>
+        <v>0.7236</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9051</v>
+        <v>0.8554</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6565</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. IBAÑEZ ZAMALLOA</t>
+          <t>J. SANTOLARIA MARTIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4188</v>
+        <v>1.124</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2171</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>2.636</v>
+        <v>0.31</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4734</v>
+        <v>1.2137</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08939999999999999</v>
+        <v>2.1586</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5628</v>
+        <v>-0.945</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1074</v>
+        <v>1.6761</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2971</v>
+        <v>1.6761</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1897</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5808</v>
+        <v>-0.4624</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2077</v>
+        <v>0.4826</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3731</v>
+        <v>-0.945</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5792</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>2.51</v>
+        <v>0.7723</v>
       </c>
       <c r="S7" t="n">
-        <v>1.313</v>
+        <v>0.1034</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6063</v>
+        <v>0.1033</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7067</v>
+        <v>0.0001</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2051</v>
+        <v>1.0976</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1465</v>
+        <v>0.9396</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0586</v>
+        <v>0.1579</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1157</v>
@@ -1078,13 +1078,13 @@
         <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1969</v>
+        <v>1.0894</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0754</v>
+        <v>0.8686</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1215</v>
+        <v>0.2208</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2277</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6047</v>
+        <v>0.5524</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0275</v>
+        <v>-0.1241</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5772</v>
+        <v>0.6765</v>
       </c>
       <c r="G9" t="n">
         <v>0.206</v>
@@ -1156,13 +1156,13 @@
         <v>0.3862</v>
       </c>
       <c r="S9" t="n">
-        <v>0.673</v>
+        <v>0.6207</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1377</v>
+        <v>-0.014</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5353</v>
+        <v>0.6347</v>
       </c>
       <c r="V9" t="n">
         <v>1.2703</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7028</v>
+        <v>-0.9386</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1177</v>
+        <v>-0.428</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5851</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5593</v>
@@ -1234,13 +1234,13 @@
         <v>0.3862</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4357</v>
+        <v>0.1999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5239</v>
+        <v>0.2137</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0882</v>
+        <v>-0.0137</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1842</v>
+        <v>-1.158</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6538</v>
+        <v>-1.702</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4695</v>
+        <v>0.544</v>
       </c>
       <c r="G11" t="n">
         <v>0.0073</v>
@@ -1312,13 +1312,13 @@
         <v>1.9308</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2261</v>
+        <v>-0.1999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3584</v>
+        <v>0.3101</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5845</v>
+        <v>-0.51</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7954</v>
+        <v>-1.3251</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4593</v>
+        <v>-2.0387</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6639</v>
+        <v>0.7136</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7318</v>
@@ -1390,13 +1390,13 @@
         <v>1.5446</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3806</v>
+        <v>0.0897</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5243</v>
+        <v>-0.1037</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1437</v>
+        <v>0.1934</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2277</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.6373</v>
+        <v>-4.6042</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0836</v>
+        <v>-0.8767</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.5537</v>
+        <v>-3.7275</v>
       </c>
       <c r="G13" t="n">
         <v>-1.1737</v>
@@ -1468,13 +1468,13 @@
         <v>0.3862</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1433</v>
+        <v>-0.1103</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1655</v>
+        <v>0.0413</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0223</v>
+        <v>-0.1516</v>
       </c>
       <c r="V13" t="n">
         <v>-2.741</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.5888</v>
+        <v>14.1408</v>
       </c>
       <c r="E14" t="n">
-        <v>10.7196</v>
+        <v>11.2716</v>
       </c>
       <c r="F14" t="n">
-        <v>2.869199999999999</v>
+        <v>2.8693</v>
       </c>
       <c r="G14" t="n">
         <v>7.622000000000002</v>
@@ -1531,7 +1531,7 @@
         <v>-5.2505</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6950000000000002</v>
+        <v>-0.695</v>
       </c>
       <c r="O14" t="n">
         <v>-4.556</v>
@@ -1546,13 +1546,13 @@
         <v>15.4462</v>
       </c>
       <c r="S14" t="n">
-        <v>6.2059</v>
+        <v>6.7576</v>
       </c>
       <c r="T14" t="n">
-        <v>4.409899999999999</v>
+        <v>4.9616</v>
       </c>
       <c r="U14" t="n">
-        <v>1.796</v>
+        <v>1.7961</v>
       </c>
       <c r="V14" t="n">
         <v>-2.1699</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8069</v>
+        <v>3.4095</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9281</v>
+        <v>1.4652</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1211</v>
+        <v>1.9442</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6484</v>
+        <v>0.8371</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4277</v>
+        <v>-0.7792</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0761</v>
+        <v>1.6163</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5185</v>
+        <v>0.286</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3316</v>
+        <v>-0.365</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1869</v>
+        <v>0.6511</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.8702</v>
+        <v>0.5511</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.7593</v>
+        <v>-0.4142</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1108</v>
+        <v>0.9653</v>
       </c>
       <c r="P15" t="n">
         <v>1.1585</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1239</v>
+        <v>1.1585</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7724</v>
+        <v>0.1862</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6339</v>
+        <v>-0.0485</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1385</v>
+        <v>0.2346</v>
       </c>
       <c r="V15" t="n">
         <v>1.2277</v>
       </c>
       <c r="W15" t="n">
-        <v>2.741</v>
+        <v>1.2277</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7489</v>
+        <v>3.1379</v>
       </c>
       <c r="E16" t="n">
-        <v>1.155</v>
+        <v>5.6178</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5939</v>
+        <v>-2.4799</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8371</v>
+        <v>0.6484</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7792</v>
+        <v>-0.4277</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6163</v>
+        <v>1.0761</v>
       </c>
       <c r="J16" t="n">
-        <v>0.286</v>
+        <v>3.5185</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.365</v>
+        <v>2.3316</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6511</v>
+        <v>1.1869</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5511</v>
+        <v>-2.8702</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4142</v>
+        <v>-2.7593</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9653</v>
+        <v>-0.1108</v>
       </c>
       <c r="P16" t="n">
         <v>1.1585</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1585</v>
+        <v>2.1239</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4744</v>
+        <v>0.1034</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3587</v>
+        <v>0.3237</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1156</v>
+        <v>-0.2203</v>
       </c>
       <c r="V16" t="n">
         <v>1.2277</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2277</v>
+        <v>2.741</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7885</v>
+        <v>1.1566</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8821</v>
+        <v>3.3992</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0936</v>
+        <v>-2.2426</v>
       </c>
       <c r="G17" t="n">
         <v>2.9287</v>
@@ -1780,13 +1780,13 @@
         <v>1.5446</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7541</v>
+        <v>-1.386</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1036</v>
+        <v>-0.5865</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6504</v>
+        <v>-0.7994</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2372</v>
+        <v>-0.1945</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6285</v>
+        <v>-1.5251</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3913</v>
+        <v>1.3306</v>
       </c>
       <c r="G18" t="n">
         <v>0.5019</v>
@@ -1858,13 +1858,13 @@
         <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.546</v>
+        <v>-0.5033</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.607</v>
+        <v>-0.5036</v>
       </c>
       <c r="U18" t="n">
-        <v>0.061</v>
+        <v>0.0002</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>F. DIAZ MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5188</v>
+        <v>-0.4448</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7826</v>
+        <v>0.3663</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7362</v>
+        <v>-0.8111</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8514</v>
+        <v>-0.5414</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7315</v>
+        <v>0.2001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1199</v>
+        <v>-0.7415</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2189</v>
+        <v>1.2809</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0968</v>
+        <v>1.9252</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1221</v>
+        <v>-0.6442</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0703</v>
+        <v>-1.8223</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8283</v>
+        <v>-1.725</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.242</v>
+        <v>-0.0973</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7377</v>
+        <v>1.9308</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1475</v>
+        <v>-0.8688</v>
       </c>
       <c r="T19" t="n">
-        <v>1.3234</v>
+        <v>-0.2349</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1759</v>
+        <v>-0.6339</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5712</v>
+        <v>0.2856</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. DIAZ MARTINEZ</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6391</v>
+        <v>-2.6042</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2542</v>
+        <v>-1.9203</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3849</v>
+        <v>-0.6839</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5414</v>
+        <v>-0.8514</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2001</v>
+        <v>-0.7315</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7415</v>
+        <v>-0.1199</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2809</v>
+        <v>0.2189</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9252</v>
+        <v>0.0968</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6442</v>
+        <v>0.1221</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8223</v>
+        <v>-1.0703</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.725</v>
+        <v>-0.8283</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0973</v>
+        <v>-0.242</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9308</v>
+        <v>1.7377</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0631</v>
+        <v>0.0622</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8554</v>
+        <v>0.1858</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2077</v>
+        <v>-0.1236</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2856</v>
+        <v>0.5712</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8075</v>
+        <v>-2.7962</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4111</v>
+        <v>0.2735</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.2187</v>
+        <v>-3.0697</v>
       </c>
       <c r="G21" t="n">
         <v>0.266</v>
@@ -2092,13 +2092,13 @@
         <v>0.5792</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1195</v>
+        <v>0.1309</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5718</v>
+        <v>0.4342</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4523</v>
+        <v>-0.3033</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8415</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5439</v>
+        <v>-3.337</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5885</v>
+        <v>-2.3817</v>
       </c>
       <c r="F22" t="n">
         <v>-0.9554</v>
@@ -2170,10 +2170,10 @@
         <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7448</v>
+        <v>-0.5379</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8829</v>
+        <v>-0.6761</v>
       </c>
       <c r="U22" t="n">
         <v>0.1381</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.431</v>
+        <v>-4.2408</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8198</v>
+        <v>-3.3027</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6112</v>
+        <v>-0.9381</v>
       </c>
       <c r="G23" t="n">
         <v>-3.8152</v>
@@ -2248,13 +2248,13 @@
         <v>1.9308</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.7968</v>
+        <v>-1.6066</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1036</v>
+        <v>-0.5865</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.6932</v>
+        <v>-1.0201</v>
       </c>
       <c r="V23" t="n">
         <v>3.1118</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.7559</v>
+        <v>-6.2966</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.1718</v>
+        <v>-4.8616</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.584</v>
+        <v>-1.4351</v>
       </c>
       <c r="G24" t="n">
         <v>-4.7312</v>
@@ -2326,13 +2326,13 @@
         <v>0.7723</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8662</v>
+        <v>-0.4069</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4139</v>
+        <v>-0.1037</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4523</v>
+        <v>-0.3033</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-13.5891</v>
+        <v>-12.2101</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8691</v>
+        <v>-2.8694</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.7199</v>
+        <v>-9.341000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-7.622100000000001</v>
@@ -2404,13 +2404,13 @@
         <v>13.5155</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.206</v>
+        <v>-4.8268</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.796</v>
+        <v>-1.7961</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.4098</v>
+        <v>-3.031000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>2.169700000000001</v>
